--- a/artfynd/A 4081-2024 artfynd.xlsx
+++ b/artfynd/A 4081-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4081-2024 artfynd.xlsx
+++ b/artfynd/A 4081-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>113680489</v>
       </c>
       <c r="B2" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -775,12 +770,12 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -789,12 +784,7 @@
         <v>113680487</v>
       </c>
       <c r="B3" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,12 +876,12 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -900,12 +890,7 @@
         <v>113680490</v>
       </c>
       <c r="B4" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,12 +982,12 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -1011,12 +996,7 @@
         <v>113680488</v>
       </c>
       <c r="B5" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,12 +1088,12 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 4081-2024 artfynd.xlsx
+++ b/artfynd/A 4081-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113680489</v>
       </c>
       <c r="B2" t="n">
-        <v>92183</v>
+        <v>92188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113680487</v>
       </c>
       <c r="B3" t="n">
-        <v>91884</v>
+        <v>91889</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113680490</v>
       </c>
       <c r="B4" t="n">
-        <v>91884</v>
+        <v>91889</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>113680488</v>
       </c>
       <c r="B5" t="n">
-        <v>91884</v>
+        <v>91889</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4081-2024 artfynd.xlsx
+++ b/artfynd/A 4081-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113680489</v>
       </c>
       <c r="B2" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113680487</v>
       </c>
       <c r="B3" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113680490</v>
       </c>
       <c r="B4" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>113680488</v>
       </c>
       <c r="B5" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4081-2024 artfynd.xlsx
+++ b/artfynd/A 4081-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113680489</v>
       </c>
       <c r="B2" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113680487</v>
       </c>
       <c r="B3" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113680490</v>
       </c>
       <c r="B4" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>113680488</v>
       </c>
       <c r="B5" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4081-2024 artfynd.xlsx
+++ b/artfynd/A 4081-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113680489</v>
       </c>
       <c r="B2" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113680487</v>
       </c>
       <c r="B3" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113680490</v>
       </c>
       <c r="B4" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>113680488</v>
       </c>
       <c r="B5" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4081-2024 artfynd.xlsx
+++ b/artfynd/A 4081-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113680489</v>
       </c>
       <c r="B2" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113680487</v>
       </c>
       <c r="B3" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113680490</v>
       </c>
       <c r="B4" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>113680488</v>
       </c>
       <c r="B5" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
